--- a/RaidenDemo/文档/配置表/SceneBgResource.xlsx
+++ b/RaidenDemo/文档/配置表/SceneBgResource.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raed96e585d0a47d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9e4c0d9e87fc48bd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1447,19 +1447,19 @@
         <x:v>forest_cloud_low</x:v>
       </x:c>
       <x:c r="G4" s="58" t="n">
-        <x:v>135</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H4" s="59" t="str">
         <x:v>forest_cloud_mid</x:v>
       </x:c>
       <x:c r="I4" s="58" t="n">
-        <x:v>165</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="J4" s="59" t="str">
         <x:v>forest_cloud_high</x:v>
       </x:c>
       <x:c r="K4" s="58" t="n">
-        <x:v>210</x:v>
+        <x:v>800</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
@@ -1480,19 +1480,19 @@
         <x:v>island_deep_sea_cloud_low</x:v>
       </x:c>
       <x:c r="G5" s="64" t="n">
-        <x:v>135</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H5" s="65" t="str">
         <x:v>island_deep_sea_cloud_middle</x:v>
       </x:c>
       <x:c r="I5" s="64" t="n">
-        <x:v>165</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="J5" s="65" t="str">
         <x:v>island_deep_sea_cloud_high</x:v>
       </x:c>
       <x:c r="K5" s="64" t="n">
-        <x:v>210</x:v>
+        <x:v>800</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
@@ -1637,6 +1637,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25cbfe00ad4949be"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9be8a03f7b414145"/>
 </x:worksheet>
 </file>